--- a/files/excel-mastery-4-1.xlsx
+++ b/files/excel-mastery-4-1.xlsx
@@ -541,7 +541,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -549,8 +549,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -647,9 +650,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -704,21 +704,12 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -731,29 +722,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
@@ -869,170 +839,282 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="25" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1041,83 +1123,15 @@
     <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="28" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準 2" xfId="2"/>
+    <cellStyle name="パーセント" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1557,177 +1571,177 @@
   <dimension ref="B2:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="2.36328125" customWidth="1" style="158" min="1" max="3"/>
-    <col width="32" customWidth="1" style="158" min="4" max="4"/>
-    <col width="16" customWidth="1" style="158" min="5" max="6"/>
-    <col width="14" customWidth="1" style="158" min="7" max="7"/>
-    <col width="10" customWidth="1" style="158" min="8" max="8"/>
+    <col width="2.36328125" customWidth="1" min="1" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.5" customHeight="1" s="158">
-      <c r="B2" s="75" t="inlineStr">
+    <row r="2" ht="19.5" customHeight="1">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>4-1. チェックセルを設ける</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="158"/>
-    <row r="4" ht="13.5" customHeight="1" s="158">
+    <row r="3" ht="13.5" customHeight="1"/>
+    <row r="4" ht="13.5" customHeight="1">
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>「別ルートで出した2つの値が一致するか」を機械的に判定。1つでも要確認なら全体を疑う。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="13.5" customHeight="1" s="158">
-      <c r="D5" s="77" t="inlineStr">
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="D5" s="66" t="inlineStr">
         <is>
           <t>一致チェック</t>
         </is>
       </c>
-      <c r="E5" s="78" t="n"/>
-      <c r="F5" s="78" t="n"/>
-      <c r="G5" s="78" t="n"/>
-      <c r="H5" s="78" t="n"/>
+      <c r="E5" s="67" t="n"/>
+      <c r="F5" s="67" t="n"/>
+      <c r="G5" s="67" t="n"/>
+      <c r="H5" s="67" t="n"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="158"/>
-    <row r="7" ht="13.5" customHeight="1" s="158">
-      <c r="D7" s="168" t="inlineStr">
+    <row r="6" ht="13.5" customHeight="1"/>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="D7" s="68" t="inlineStr">
         <is>
           <t>チェック項目</t>
         </is>
       </c>
-      <c r="E7" s="168" t="inlineStr">
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>値A</t>
         </is>
       </c>
-      <c r="F7" s="168" t="inlineStr">
+      <c r="F7" s="68" t="inlineStr">
         <is>
           <t>値B</t>
         </is>
       </c>
-      <c r="G7" s="168" t="inlineStr">
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>差(A−B)</t>
         </is>
       </c>
-      <c r="H7" s="168" t="inlineStr">
+      <c r="H7" s="68" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="158">
-      <c r="D8" s="80" t="inlineStr">
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="D8" s="69" t="inlineStr">
         <is>
           <t>月次合計 = 年次合計</t>
         </is>
       </c>
-      <c r="E8" s="81" t="n">
+      <c r="E8" s="70" t="n">
         <v>84000000</v>
       </c>
-      <c r="F8" s="81" t="n">
+      <c r="F8" s="70" t="n">
         <v>84000000</v>
       </c>
-      <c r="G8" s="189">
+      <c r="G8" s="191">
         <f>E8-F8</f>
         <v/>
       </c>
-      <c r="H8" s="98">
+      <c r="H8" s="87">
         <f>IF(ABS(G8)&lt;1,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="158">
-      <c r="D9" s="83" t="inlineStr">
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="D9" s="72" t="inlineStr">
         <is>
           <t>部門別売上合計 = 全社売上</t>
         </is>
       </c>
-      <c r="E9" s="84" t="n">
+      <c r="E9" s="73" t="n">
         <v>84000000</v>
       </c>
-      <c r="F9" s="84" t="n">
+      <c r="F9" s="73" t="n">
         <v>84000000</v>
       </c>
-      <c r="G9" s="190">
+      <c r="G9" s="192">
         <f>E9-F9</f>
         <v/>
       </c>
-      <c r="H9" s="99">
+      <c r="H9" s="88">
         <f>IF(ABS(G9)&lt;1,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="158">
-      <c r="D10" s="83" t="inlineStr">
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="D10" s="72" t="inlineStr">
         <is>
           <t>元データ件数 = 集計後件数</t>
         </is>
       </c>
-      <c r="E10" s="101" t="n">
+      <c r="E10" s="90" t="n">
         <v>1200</v>
       </c>
-      <c r="F10" s="101" t="n">
+      <c r="F10" s="90" t="n">
         <v>1200</v>
       </c>
-      <c r="G10" s="190">
+      <c r="G10" s="192">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="H10" s="99">
+      <c r="H10" s="88">
         <f>IF(ABS(G10)&lt;1,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="13.5" customHeight="1" s="158">
-      <c r="D11" s="83" t="inlineStr">
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="D11" s="72" t="inlineStr">
         <is>
           <t>税抜×1.1 = 税込</t>
         </is>
       </c>
-      <c r="E11" s="84" t="n">
+      <c r="E11" s="73" t="n">
         <v>92400000</v>
       </c>
-      <c r="F11" s="84" t="n">
+      <c r="F11" s="73" t="n">
         <v>92400000</v>
       </c>
-      <c r="G11" s="190">
+      <c r="G11" s="192">
         <f>E11-F11</f>
         <v/>
       </c>
-      <c r="H11" s="99">
+      <c r="H11" s="88">
         <f>IF(ABS(G11)&lt;1,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="158">
-      <c r="D12" s="83" t="inlineStr">
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="D12" s="72" t="inlineStr">
         <is>
           <t>構成比の合計 = 100%</t>
         </is>
       </c>
-      <c r="E12" s="191" t="n">
+      <c r="E12" s="193" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="191" t="n">
+      <c r="F12" s="193" t="n">
         <v>0.99834336</v>
       </c>
-      <c r="G12" s="190">
+      <c r="G12" s="192">
         <f>E12-F12</f>
         <v/>
       </c>
-      <c r="H12" s="99">
+      <c r="H12" s="88">
         <f>IF(ABS(G12)&lt;0.0001,"OK","要確認")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="13.5" customHeight="1" s="158"/>
-    <row r="14" ht="13.5" customHeight="1" s="158">
-      <c r="D14" s="76" t="n"/>
+    <row r="13" ht="13.5" customHeight="1"/>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="D14" s="65" t="n"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1" s="158"/>
+    <row r="15" ht="13.5" customHeight="1"/>
   </sheetData>
   <conditionalFormatting sqref="H8:H12">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="1">

--- a/files/excel-mastery-4-1.xlsx
+++ b/files/excel-mastery-4-1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-1605" yWindow="-16320" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="280" windowWidth="17320" windowHeight="10400" tabRatio="773" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="4-1_チェックセル" sheetId="1" state="visible" r:id="rId1"/>
@@ -553,7 +553,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1049,74 +1049,77 @@
     <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="28" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1644,7 +1647,7 @@
       <c r="F8" s="70" t="n">
         <v>84000000</v>
       </c>
-      <c r="G8" s="191">
+      <c r="G8" s="192">
         <f>E8-F8</f>
         <v/>
       </c>
@@ -1665,7 +1668,7 @@
       <c r="F9" s="73" t="n">
         <v>84000000</v>
       </c>
-      <c r="G9" s="192">
+      <c r="G9" s="193">
         <f>E9-F9</f>
         <v/>
       </c>
@@ -1686,7 +1689,7 @@
       <c r="F10" s="90" t="n">
         <v>1200</v>
       </c>
-      <c r="G10" s="192">
+      <c r="G10" s="193">
         <f>E10-F10</f>
         <v/>
       </c>
@@ -1707,7 +1710,7 @@
       <c r="F11" s="73" t="n">
         <v>92400000</v>
       </c>
-      <c r="G11" s="192">
+      <c r="G11" s="193">
         <f>E11-F11</f>
         <v/>
       </c>
@@ -1722,13 +1725,13 @@
           <t>構成比の合計 = 100%</t>
         </is>
       </c>
-      <c r="E12" s="193" t="n">
+      <c r="E12" s="194" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="193" t="n">
+      <c r="F12" s="194" t="n">
         <v>0.99834336</v>
       </c>
-      <c r="G12" s="192">
+      <c r="G12" s="193">
         <f>E12-F12</f>
         <v/>
       </c>
